--- a/01_Tender_Log/Tender_Dashboard_v2.xlsx
+++ b/01_Tender_Log/Tender_Dashboard_v2.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -1469,7 +1469,7 @@
         <is>
           <t>High context overlap: power station, plant, treatment
 [Score: 7.2/10 | Priority: HIGH]
-✅ RECOMMENDED - Good opportunity, prepare bid</t>
+✅ RECOMMENDED - Good opportunity, prepare bid [Phase 2: Competence Mismatch]</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -1544,7 +1544,7 @@
         <is>
           <t>Context (power station) + Supporting signal (ro)
 [Score: 8.0/10 | Priority: HIGH]
-🔥 PRIORITY BID - Strong fit, pursue immediately</t>
+🔥 PRIORITY BID - Strong fit, pursue immediately [Phase 2: Competence Mismatch]</t>
         </is>
       </c>
       <c r="N15" s="1" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -1619,7 +1619,7 @@
         <is>
           <t>Context (power station) + Supporting signal (ro)
 [Score: 7.2/10 | Priority: HIGH]
-✅ RECOMMENDED - Good opportunity, prepare bid</t>
+✅ RECOMMENDED - Good opportunity, prepare bid [Phase 2: Competence Mismatch]</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr">

--- a/01_Tender_Log/Tender_Dashboard_v2.xlsx
+++ b/01_Tender_Log/Tender_Dashboard_v2.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TES</t>
+          <t>MEXEL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,22 +603,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NT002 - Pump Refurbishment and Mechanical Repairs</t>
+          <t>NT004 - Boiler Water Treatment Services</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>City of Johannesburg</t>
+          <t>Sasol</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phakathi</t>
+          <t>MEXEL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Petrochemical</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -639,7 +639,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Phakathi override keyword detected: 'pump'</t>
+          <t>TES override keyword detected: 'boiler'</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>NT002</t>
+          <t>NT004</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -667,973 +667,6 @@
           <t>2025-11-27</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NT003 - Switchgear Panel Upgrade MV Distribution</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Transnet</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Phakathi</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Phakathi override keyword detected: 'switchgear'</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>NT003</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NT004 - Boiler Water Treatment Services</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sasol</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TES</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Petrochemical</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>TES override keyword detected: 'boiler'</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>NT004</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NT005 - Fabrication of Structural Steelwork</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Anglo American</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Phakathi</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Phakathi override keyword detected: 'fabrication'</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>NT005</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EKU - Open Tenders (Over R750 000)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>City of Ekurhuleni</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>City of Ekurhuleni</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>07/11/2025</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>No clear classification signals detected</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>EKU</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>E1743CXMWPN - Transactional Advisor Services to conduct feasibility study for establishment of the BESS manufactur</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>TES</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Eskom (Eskom)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan-13</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Prepare Bid</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>TES keyword score: 1
-[Score: 6.1/10 | Priority: MEDIUM]
-✅ RECOMMENDED - Good opportunity, prepare bid</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>E1743CXMWPN</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>E2129CXMWP - SUPPLY AND DELIVERY OF IT PERIPHERALS TO ALL ESKOM DIVISIONS AS AN WHEN REQUIRED FOR A PERIOD OF FIV</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>TES</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Eskom (Eskom)</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan-15</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Prepare Bid</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>TES keyword score: 1
-[Score: 6.1/10 | Priority: MEDIUM]
-✅ RECOMMENDED - Good opportunity, prepare bid</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>E2129CXMWP</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>E2319GCDMWP - Eskom is seeking an independent accounting firm to review and assess Eskom Treasury’s hedge accounti</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>TES</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Eskom (Eskom)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan-15</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Prepare Bid</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>TES keyword score: 1
-[Score: 6.1/10 | Priority: MEDIUM]
-✅ RECOMMENDED - Good opportunity, prepare bid</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>E2319GCDMWP</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>E2160CXCTS - The Provision of Job Boards for Eskom to Place and Manage Job Adverts</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>TES</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Eskom (Eskom)</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan-16</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Prepare Bid</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>TES keyword score: 1
-[Score: 6.1/10 | Priority: MEDIUM]
-✅ RECOMMENDED - Good opportunity, prepare bid</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>E2160CXCTS</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>E2279GXMPKRI - Detail design, manufacturing, construction, factory acceptance testing, transporting, offloading, in</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>MEXEL</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>Eskom (Power)</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>2026-Jan-22</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>URGENT BID</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>Mexel/TES keyword score: 1
-[Score: 7.2/10 | Priority: HIGH]
-✅ RECOMMENDED - Good opportunity, prepare bid</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>E2279GXMPKRI</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="P12" s="1" t="n"/>
-      <c r="Q12" s="1" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E2247GXMPCAM - Service, Repair and Calibration of all Test &amp; Measuring Equipment for the 48 months at Camden Power </t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>MEXEL</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>Eskom (Power)</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>2026-Jan-22</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>URGENT BID</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>Mexel/TES keyword score: 1
-[Score: 7.2/10 | Priority: HIGH]
-✅ RECOMMENDED - Good opportunity, prepare bid</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>E2247GXMPCAM</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="n"/>
-      <c r="Q13" s="1" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>MPHEN11110GXAWARD - Award of Operation and management of the Sewage treatment plant at Hendrina Power Station</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>MEXEL</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>Eskom (Power)</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>2026-02-03T10:00:00</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>URGENT BID</t>
-        </is>
-      </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>High context overlap: power station, plant, treatment
-[Score: 7.2/10 | Priority: HIGH]
-✅ RECOMMENDED - Good opportunity, prepare bid [Phase 2: Competence Mismatch]</t>
-        </is>
-      </c>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>MPHEN11110GXAWARD</t>
-        </is>
-      </c>
-      <c r="O14" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="P14" s="1" t="n"/>
-      <c r="Q14" s="1" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>MPKUS11014GXR1 - The Provision of Operating and Commissioning Support Resources for Kusile Power Station for a period</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>MEXEL</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Eskom (Power)</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>2029-08-15T10:00:00</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>URGENT BID</t>
-        </is>
-      </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>Context (power station) + Supporting signal (ro)
-[Score: 8.0/10 | Priority: HIGH]
-🔥 PRIORITY BID - Strong fit, pursue immediately [Phase 2: Competence Mismatch]</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>MPKUS11014GXR1</t>
-        </is>
-      </c>
-      <c r="O15" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="P15" s="1" t="n"/>
-      <c r="Q15" s="1" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E2138GXMWP - Request For Information (RFI) for South African Hydroelectric Power Station Development.</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>Eskom</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>MEXEL</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>Eskom (Power)</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-30T10:00:00</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>URGENT BID</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>Context (power station) + Supporting signal (ro)
-[Score: 7.2/10 | Priority: HIGH]
-✅ RECOMMENDED - Good opportunity, prepare bid [Phase 2: Competence Mismatch]</t>
-        </is>
-      </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t>E2138GXMWP</t>
-        </is>
-      </c>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="P16" s="1" t="n"/>
-      <c r="Q16" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
